--- a/AtchisonRegime/Outputs/China/df_regZScores_China.xlsx
+++ b/AtchisonRegime/Outputs/China/df_regZScores_China.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1982,7 +1982,7 @@
         <v>-0.7573208650167998</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.2748089633951488</v>
+        <v>-0.3947190755637957</v>
       </c>
       <c r="D91" t="n">
         <v>-2.186171825947814</v>
@@ -1999,7 +1999,7 @@
         <v>-0.6936456221255526</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.2279126352522796</v>
+        <v>-0.2155123505395301</v>
       </c>
       <c r="D92" t="n">
         <v>-2.121261731515194</v>
@@ -2016,7 +2016,7 @@
         <v>-0.6126315461159145</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.1571771349177754</v>
+        <v>-0.1369821570201432</v>
       </c>
       <c r="D93" t="n">
         <v>-2.092739462104736</v>
@@ -2033,7 +2033,7 @@
         <v>-0.5084519801903494</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.05568094083677352</v>
+        <v>-0.03027941206202257</v>
       </c>
       <c r="D94" t="n">
         <v>-2.065545548710271</v>
@@ -2050,7 +2050,7 @@
         <v>-0.4336219428364395</v>
       </c>
       <c r="C95" t="n">
-        <v>0.06489742026200002</v>
+        <v>0.09304350422744435</v>
       </c>
       <c r="D95" t="n">
         <v>-1.968859632598976</v>
@@ -2067,7 +2067,7 @@
         <v>-0.4657215735652193</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1759128359355281</v>
+        <v>0.2054174209692945</v>
       </c>
       <c r="D96" t="n">
         <v>-1.832013160230655</v>
@@ -2084,7 +2084,7 @@
         <v>-0.5505039986564023</v>
       </c>
       <c r="C97" t="n">
-        <v>0.2313892661628568</v>
+        <v>0.2757055266963961</v>
       </c>
       <c r="D97" t="n">
         <v>-1.827837999373457</v>
@@ -2101,7 +2101,7 @@
         <v>-0.6105568779169617</v>
       </c>
       <c r="C98" t="n">
-        <v>0.277805270977266</v>
+        <v>0.3123296962227394</v>
       </c>
       <c r="D98" t="n">
         <v>-2.016958559004275</v>
@@ -2118,7 +2118,7 @@
         <v>-0.5325494453957975</v>
       </c>
       <c r="C99" t="n">
-        <v>0.2780095875200979</v>
+        <v>0.3223443003377225</v>
       </c>
       <c r="D99" t="n">
         <v>-2.228635352098381</v>
@@ -2135,7 +2135,7 @@
         <v>-0.7633229331216338</v>
       </c>
       <c r="C100" t="n">
-        <v>0.2782716760091419</v>
+        <v>0.3213732415420884</v>
       </c>
       <c r="D100" t="n">
         <v>-2.323392764932454</v>
@@ -2149,16 +2149,33 @@
         <v>45747</v>
       </c>
       <c r="B101" t="n">
-        <v>-0.9436146564825021</v>
+        <v>-0.7835479487520001</v>
       </c>
       <c r="C101" t="n">
-        <v>0.2879412727724567</v>
+        <v>0.3105360517581144</v>
       </c>
       <c r="D101" t="n">
         <v>-2.142319343038797</v>
       </c>
       <c r="E101" t="n">
         <v>-1.677345613784312</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B102" t="n">
+        <v>-0.9346642881743581</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.2967768877878058</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-1.963471017062621</v>
+      </c>
+      <c r="E102" t="n">
+        <v>-1.573545865216119</v>
       </c>
     </row>
   </sheetData>
